--- a/Sample_run/1/student/DuyCNHE187327/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/DuyCNHE187327/TC1/GradeDetail.xlsx
@@ -918,7 +918,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R14"/>
+  <x:dimension ref="A1:R13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1044,7 +1044,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1103,7 +1103,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1156,7 +1156,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1327,7 +1327,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1380,7 +1380,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1439,7 +1439,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1492,7 +1492,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1551,7 +1551,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>52</x:v>
@@ -1589,10 +1589,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
         <x:v>44</x:v>
@@ -1604,7 +1604,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>39796</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1645,83 +1645,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>39796</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+        <x:v>42860</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:18">
-      <x:c r="A14" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q14" s="0">
-        <x:v>39796</x:v>
-      </x:c>
-      <x:c r="R14" s="3" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
